--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92570491552</v>
+        <v>46157.93105669018</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105669018</v>
+        <v>46157.93176645556</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93176645556</v>
+        <v>46157.93401891852</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401891852</v>
+        <v>46157.93719972286</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93719972286</v>
+        <v>46158.28217981339</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217981339</v>
+        <v>46158.29686908321</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29686908321</v>
+        <v>46158.29817032249</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29817032249</v>
+        <v>46158.33389105495</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33389105495</v>
+        <v>46158.36858861733</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858861733</v>
+        <v>46158.37289560871</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
